--- a/latest_yoco_products.xlsx
+++ b/latest_yoco_products.xlsx
@@ -125,6 +125,116 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026/02/27</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>15:32:25</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Coke Cherry</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>vjgpjmzhsj</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Cool Drinks</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026/02/27</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>15:32:25</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Coke</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>wxxhfhspjr</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="I3" t="n">
+        <v>22.82</v>
+      </c>
+      <c r="J3" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Cool Drinks</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/latest_yoco_products.xlsx
+++ b/latest_yoco_products.xlsx
@@ -133,36 +133,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15:32:25</t>
+          <t>15:42:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Coke Cherry</t>
+          <t>Smash Burger (Spicy Smash)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>vjgpjmzhsj</t>
+          <t>PLU-1001-1</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>1.0</v>
       </c>
       <c r="F2" t="n">
-        <v>40.0</v>
+        <v>99.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
       </c>
       <c r="H2" t="n">
-        <v>21.2</v>
+        <v>9.55</v>
       </c>
       <c r="I2" t="n">
-        <v>18.8</v>
+        <v>89.45</v>
       </c>
       <c r="J2" t="n">
-        <v>40.0</v>
+        <v>99.0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -171,7 +171,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Cool Drinks</t>
+          <t>Burgers</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -188,48 +188,158 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15:32:25</t>
+          <t>15:42:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Coke</t>
+          <t>Smash Burger Special (Classic Smash)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>wxxhfhspjr</t>
+          <t>mxvnggstlv</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>1.0</v>
       </c>
       <c r="F3" t="n">
-        <v>28.0</v>
+        <v>99.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
       </c>
       <c r="H3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="I3" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="J3" t="n">
+        <v>99.0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>CLASSIC SPECIAL</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026/02/27</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>15:32:25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Coke Cherry</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>vjgpjmzhsj</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Cool Drinks</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026/02/27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15:32:25</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Coke</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>wxxhfhspjr</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H5" t="n">
         <v>5.18</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I5" t="n">
         <v>22.82</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J5" t="n">
         <v>28.0</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Cool Drinks</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/latest_yoco_products.xlsx
+++ b/latest_yoco_products.xlsx
@@ -133,36 +133,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15:42:14</t>
+          <t>15:45:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Smash Burger (Spicy Smash)</t>
+          <t>Caps</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PLU-1001-1</t>
+          <t>tjfxmzmcxz</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>1.0</v>
       </c>
       <c r="F2" t="n">
-        <v>99.0</v>
+        <v>150.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
       </c>
       <c r="H2" t="n">
-        <v>9.55</v>
+        <v>0.0</v>
       </c>
       <c r="I2" t="n">
-        <v>89.45</v>
+        <v>150.0</v>
       </c>
       <c r="J2" t="n">
-        <v>99.0</v>
+        <v>150.0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -171,7 +171,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Burgers</t>
+          <t>Merchandise</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -188,36 +188,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15:42:14</t>
+          <t>15:45:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Smash Burger Special (Classic Smash)</t>
+          <t>SNACK WRAP</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>mxvnggstlv</t>
+          <t>klfgpklmkl</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>1.0</v>
       </c>
       <c r="F3" t="n">
-        <v>99.0</v>
+        <v>0.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
       </c>
       <c r="H3" t="n">
-        <v>9.02</v>
+        <v>395.3</v>
       </c>
       <c r="I3" t="n">
-        <v>89.98</v>
+        <v>-395.3</v>
       </c>
       <c r="J3" t="n">
-        <v>99.0</v>
+        <v>0.0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -226,7 +226,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLASSIC SPECIAL</t>
+          <t>Merchandise</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -243,36 +243,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:32:25</t>
+          <t>15:45:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Coke Cherry</t>
+          <t>Smash Burger (Spicy Smash)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>vjgpjmzhsj</t>
+          <t>PLU-1001-1</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>1.0</v>
       </c>
       <c r="F4" t="n">
-        <v>40.0</v>
+        <v>99.0</v>
       </c>
       <c r="G4" t="n">
         <v>0.0</v>
       </c>
       <c r="H4" t="n">
-        <v>21.2</v>
+        <v>9.55</v>
       </c>
       <c r="I4" t="n">
-        <v>18.8</v>
+        <v>89.45</v>
       </c>
       <c r="J4" t="n">
-        <v>40.0</v>
+        <v>99.0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cool Drinks</t>
+          <t>Burgers</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -298,48 +298,268 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>15:45:19</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Coke Cherry</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>vjgpjmzhsj</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Cool Drinks</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026/02/27</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15:42:14</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Smash Burger (Spicy Smash)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PLU-1001-1</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>99.0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>89.45</v>
+      </c>
+      <c r="J6" t="n">
+        <v>99.0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Burgers</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026/02/27</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15:42:14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Smash Burger Special (Classic Smash)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>mxvnggstlv</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>99.0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="I7" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="J7" t="n">
+        <v>99.0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>CLASSIC SPECIAL</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026/02/27</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>15:32:25</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Coke Cherry</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>vjgpjmzhsj</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Cool Drinks</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026/02/27</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>15:32:25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Coke</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>wxxhfhspjr</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="E9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F9" t="n">
         <v>28.0</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="G9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H9" t="n">
         <v>5.18</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I9" t="n">
         <v>22.82</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J9" t="n">
         <v>28.0</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Cool Drinks</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/latest_yoco_products.xlsx
+++ b/latest_yoco_products.xlsx
@@ -124,6 +124,11 @@
           <t>Brand</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -133,36 +138,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15:45:48</t>
+          <t>16:24:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Caps</t>
+          <t>Coke</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>tjfxmzmcxz</t>
+          <t>wxxhfhspjr</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>1.0</v>
       </c>
       <c r="F2" t="n">
-        <v>150.0</v>
+        <v>28.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0</v>
+        <v>5.18</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0</v>
+        <v>22.82</v>
       </c>
       <c r="J2" t="n">
-        <v>150.0</v>
+        <v>28.0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -171,12 +176,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Merchandise</t>
+          <t>Cool Drinks</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
           <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -188,36 +198,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15:45:19</t>
+          <t>16:23:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SNACK WRAP</t>
+          <t>Coke</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>klfgpklmkl</t>
+          <t>wxxhfhspjr</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>1.0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0</v>
+        <v>28.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
       </c>
       <c r="H3" t="n">
-        <v>395.3</v>
+        <v>5.18</v>
       </c>
       <c r="I3" t="n">
-        <v>-395.3</v>
+        <v>22.82</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0</v>
+        <v>28.0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -226,12 +236,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Merchandise</t>
+          <t>Cool Drinks</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
           <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Bar</t>
         </is>
       </c>
     </row>
@@ -243,36 +258,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:45:19</t>
+          <t>15:45:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Smash Burger (Spicy Smash)</t>
+          <t>Caps</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PLU-1001-1</t>
+          <t>tjfxmzmcxz</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>1.0</v>
       </c>
       <c r="F4" t="n">
-        <v>99.0</v>
+        <v>150.0</v>
       </c>
       <c r="G4" t="n">
         <v>0.0</v>
       </c>
       <c r="H4" t="n">
-        <v>9.55</v>
+        <v>0.0</v>
       </c>
       <c r="I4" t="n">
-        <v>89.45</v>
+        <v>150.0</v>
       </c>
       <c r="J4" t="n">
-        <v>99.0</v>
+        <v>150.0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -281,10 +296,15 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Burgers</t>
+          <t>Merchandise</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -303,31 +323,31 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Coke Cherry</t>
+          <t>SNACK WRAP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>vjgpjmzhsj</t>
+          <t>klfgpklmkl</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>1.0</v>
       </c>
       <c r="F5" t="n">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="G5" t="n">
         <v>0.0</v>
       </c>
       <c r="H5" t="n">
-        <v>21.2</v>
+        <v>395.3</v>
       </c>
       <c r="I5" t="n">
-        <v>18.8</v>
+        <v>-395.3</v>
       </c>
       <c r="J5" t="n">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -336,10 +356,15 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cool Drinks</t>
+          <t>Merchandise</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -353,7 +378,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:42:14</t>
+          <t>15:45:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -399,6 +424,11 @@
           <t/>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -408,36 +438,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:42:14</t>
+          <t>15:45:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Smash Burger Special (Classic Smash)</t>
+          <t>Coke Cherry</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>mxvnggstlv</t>
+          <t>vjgpjmzhsj</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>1.0</v>
       </c>
       <c r="F7" t="n">
-        <v>99.0</v>
+        <v>40.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
       </c>
       <c r="H7" t="n">
-        <v>9.02</v>
+        <v>21.2</v>
       </c>
       <c r="I7" t="n">
-        <v>89.98</v>
+        <v>18.8</v>
       </c>
       <c r="J7" t="n">
-        <v>99.0</v>
+        <v>40.0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -446,10 +476,15 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLASSIC SPECIAL</t>
+          <t>Cool Drinks</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -463,36 +498,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15:32:25</t>
+          <t>15:42:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Coke Cherry</t>
+          <t>Smash Burger (Spicy Smash)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>vjgpjmzhsj</t>
+          <t>PLU-1001-1</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>1.0</v>
       </c>
       <c r="F8" t="n">
-        <v>40.0</v>
+        <v>99.0</v>
       </c>
       <c r="G8" t="n">
         <v>0.0</v>
       </c>
       <c r="H8" t="n">
-        <v>21.2</v>
+        <v>9.55</v>
       </c>
       <c r="I8" t="n">
-        <v>18.8</v>
+        <v>89.45</v>
       </c>
       <c r="J8" t="n">
-        <v>40.0</v>
+        <v>99.0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -501,10 +536,15 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cool Drinks</t>
+          <t>Burgers</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -518,48 +558,173 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>15:42:14</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Smash Burger Special (Classic Smash)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>mxvnggstlv</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>99.0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="I9" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="J9" t="n">
+        <v>99.0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>CLASSIC SPECIAL</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026/02/27</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>15:32:25</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Coke Cherry</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>vjgpjmzhsj</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Cool Drinks</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026/02/27</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15:32:25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Coke</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>wxxhfhspjr</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="E11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F11" t="n">
         <v>28.0</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H11" t="n">
         <v>5.18</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>22.82</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>28.0</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>Cool Drinks</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t/>
         </is>
